--- a/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2021_T3_0.xlsx
+++ b/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2021_T3_0.xlsx
@@ -57,7 +57,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>71</t>
+    <t>65</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -69,64 +69,64 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>1.317</t>
-  </si>
-  <si>
-    <t>(0.244)</t>
-  </si>
-  <si>
-    <t>7.887</t>
-  </si>
-  <si>
-    <t>(0.978)</t>
-  </si>
-  <si>
-    <t>3.110</t>
-  </si>
-  <si>
-    <t>(0.853)</t>
-  </si>
-  <si>
-    <t>14.020</t>
-  </si>
-  <si>
-    <t>(2.329)</t>
-  </si>
-  <si>
-    <t>1.788</t>
-  </si>
-  <si>
-    <t>(0.250)</t>
-  </si>
-  <si>
-    <t>10.831</t>
-  </si>
-  <si>
-    <t>(1.344)</t>
-  </si>
-  <si>
-    <t>7.129</t>
-  </si>
-  <si>
-    <t>(1.918)</t>
-  </si>
-  <si>
-    <t>0.678</t>
-  </si>
-  <si>
-    <t>(0.200)</t>
-  </si>
-  <si>
-    <t>13.736</t>
-  </si>
-  <si>
-    <t>(1.663)</t>
-  </si>
-  <si>
-    <t>14.949</t>
-  </si>
-  <si>
-    <t>(3.397)</t>
+    <t>1.438</t>
+  </si>
+  <si>
+    <t>(0.262)</t>
+  </si>
+  <si>
+    <t>8.615</t>
+  </si>
+  <si>
+    <t>(1.022)</t>
+  </si>
+  <si>
+    <t>2.448</t>
+  </si>
+  <si>
+    <t>(0.336)</t>
+  </si>
+  <si>
+    <t>10.524</t>
+  </si>
+  <si>
+    <t>(1.653)</t>
+  </si>
+  <si>
+    <t>1.725</t>
+  </si>
+  <si>
+    <t>(0.218)</t>
+  </si>
+  <si>
+    <t>11.723</t>
+  </si>
+  <si>
+    <t>(1.416)</t>
+  </si>
+  <si>
+    <t>4.354</t>
+  </si>
+  <si>
+    <t>(1.311)</t>
+  </si>
+  <si>
+    <t>0.560</t>
+  </si>
+  <si>
+    <t>(0.132)</t>
+  </si>
+  <si>
+    <t>11.704</t>
+  </si>
+  <si>
+    <t>(1.355)</t>
+  </si>
+  <si>
+    <t>9.569</t>
+  </si>
+  <si>
+    <t>(2.239)</t>
   </si>
   <si>
     <t>45</t>
@@ -198,7 +198,7 @@
     <t>(2.922)</t>
   </si>
   <si>
-    <t>116</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -210,34 +210,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.338</t>
-  </si>
-  <si>
-    <t>2.424</t>
-  </si>
-  <si>
-    <t>2.406*</t>
-  </si>
-  <si>
-    <t>-0.087</t>
-  </si>
-  <si>
-    <t>0.071</t>
-  </si>
-  <si>
-    <t>0.569</t>
-  </si>
-  <si>
-    <t>-2.529</t>
-  </si>
-  <si>
-    <t>-0.373</t>
-  </si>
-  <si>
-    <t>1.553</t>
-  </si>
-  <si>
-    <t>-1.705</t>
+    <t>0.216</t>
+  </si>
+  <si>
+    <t>1.696</t>
+  </si>
+  <si>
+    <t>3.068***</t>
+  </si>
+  <si>
+    <t>3.409</t>
+  </si>
+  <si>
+    <t>0.134</t>
+  </si>
+  <si>
+    <t>-0.323</t>
+  </si>
+  <si>
+    <t>0.246</t>
+  </si>
+  <si>
+    <t>-0.255</t>
+  </si>
+  <si>
+    <t>3.584</t>
+  </si>
+  <si>
+    <t>3.675</t>
   </si>
 </sst>
 </file>
